--- a/hourly datasets/cap_gen_year17final.xlsx
+++ b/hourly datasets/cap_gen_year17final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1032715332661945</v>
+        <v>0.1024509371948067</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.123544959004684</v>
+        <v>0.1251618907786477</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2268164922708785</v>
+        <v>0.2276128279734544</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1125071070265921</v>
+        <v>0.1409700663108019</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2157786402927865</v>
+        <v>0.2434210035056086</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04584762580201045</v>
+        <v>0.03931045717140182</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004884665086340472</v>
+        <v>0.004286792376561793</v>
       </c>
       <c r="D5" t="n">
-        <v>8.074458152572564</v>
+        <v>7.860018660693552</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05013392399081189</v>
+        <v>0.04858863438849403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03626765548662099</v>
+        <v>0.03090282406336579</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0554275961173997</v>
+        <v>0.04771809027943816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1491191590682049</v>
+        <v>0.1417613943662085</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03483020773375735</v>
+        <v>0.0272529923045134</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +567,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1381017409999518</v>
+        <v>0.1297039294993201</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01866757594154206</v>
+        <v>0.009373491403090836</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002098370891433816</v>
+        <v>0.001078042523813238</v>
       </c>
       <c r="D7" t="n">
-        <v>2.705064845679695</v>
+        <v>2.239829610691232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008510740238794712</v>
+        <v>0.004626182562008549</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01454797859067791</v>
+        <v>0.007254812198671192</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02278717329240586</v>
+        <v>0.01149217060751044</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1219391092077365</v>
+        <v>0.1118244285978975</v>
       </c>
     </row>
     <row r="8">
@@ -605,15 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01678749391398004</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>0.007732666289601032</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.001051449239383792</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.923073323159804</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.003703679840398062</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005668510802046192</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.009796821777155988</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.1200590271801745</v>
+        <v>0.1101836034844077</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01148705543886069</v>
+        <v>0.002496623643887608</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001817406281004231</v>
+        <v>0.00097438860492936</v>
       </c>
       <c r="D9" t="n">
-        <v>2.084904913975639</v>
+        <v>1.262063716918347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008441666954877369</v>
+        <v>0.00274644758770072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007919437685998357</v>
+        <v>0.0005818982634786801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01505467319172316</v>
+        <v>0.004411349024296561</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1147585887050551</v>
+        <v>0.1049475608386943</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01155506298580298</v>
+        <v>0.002488961979316782</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002082678145171691</v>
+        <v>0.001101856956930826</v>
       </c>
       <c r="D10" t="n">
-        <v>2.107974717519345</v>
+        <v>1.338429213075876</v>
       </c>
       <c r="E10" t="n">
-        <v>0.009045247916819056</v>
+        <v>0.002858187573231679</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007467477304198136</v>
+        <v>0.0003243229445220957</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01564264866740796</v>
+        <v>0.004653601014111524</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1148265962519974</v>
+        <v>0.1049398991741235</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02972441137369737</v>
+        <v>0.02958425060836664</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1329959446398918</v>
+        <v>0.1320351878031733</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05409485438562589</v>
+        <v>0.05239004873669086</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1573663876518203</v>
+        <v>0.1548409859314976</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06918147161944022</v>
+        <v>0.06683705317371819</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1724530048856347</v>
+        <v>0.1692879903685249</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08072206526740502</v>
+        <v>0.07760570208109278</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1839935985335995</v>
+        <v>0.1800566392758995</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08619898135964785</v>
+        <v>0.08287245049233326</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1894705146258423</v>
+        <v>0.18532338768714</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08985738308665765</v>
+        <v>0.08797747845923434</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1931289163528521</v>
+        <v>0.190428415654041</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09408923803573851</v>
+        <v>0.09169169449991302</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.197360771301933</v>
+        <v>0.1941426316947197</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1032715332661945</v>
+        <v>-0.1024509371948067</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008905996699974422</v>
+        <v>0.008618418715896685</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.05966684785116</v>
+        <v>-18.87795558944316</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02685169165100391</v>
+        <v>0.0283273034693172</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.120772599487219</v>
+        <v>-0.1193752552478169</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08577046704517004</v>
+        <v>-0.08552661914179618</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -833,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09406115305583133</v>
+        <v>0.09205560835761636</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1973326863220258</v>
+        <v>0.1945065455524231</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09819629145515409</v>
+        <v>0.09515115887834853</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2014678247213486</v>
+        <v>0.1976020960731552</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1016710335447454</v>
+        <v>0.09944049037465662</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2049425668109399</v>
+        <v>0.2018914275694633</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +897,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1058913419359381</v>
+        <v>0.1035047637157237</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +905,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2091628752021325</v>
+        <v>0.2059557009105304</v>
       </c>
     </row>
     <row r="23">
@@ -905,25 +915,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1096621026567973</v>
+        <v>0.1077829928986616</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007196970191805244</v>
+        <v>0.006749219018021481</v>
       </c>
       <c r="D23" t="n">
-        <v>27.19819957207644</v>
+        <v>27.09652401640841</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04345474295017757</v>
+        <v>0.04262004030880342</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09551341072141653</v>
+        <v>0.09451233458833359</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1238107945921782</v>
+        <v>0.1210536512089894</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2129336359229918</v>
+        <v>0.2102339300934683</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +943,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1131890454873457</v>
+        <v>0.1116297935099695</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007069284488701446</v>
+        <v>0.006717705687251152</v>
       </c>
       <c r="D24" t="n">
-        <v>27.99589419668919</v>
+        <v>27.94997700172785</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03090247037235266</v>
+        <v>0.03005962000518489</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09928944041638178</v>
+        <v>0.09841973565885995</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1270886505583096</v>
+        <v>0.1248398513610787</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2164605787535401</v>
+        <v>0.2140807307047762</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +971,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1155133960877915</v>
+        <v>0.1139216978492915</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007144910753670359</v>
+        <v>0.006884768854934427</v>
       </c>
       <c r="D25" t="n">
-        <v>29.10440059802164</v>
+        <v>29.07659349030482</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04618075995359579</v>
+        <v>0.04713455382755396</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1014584394361259</v>
+        <v>0.1003765638568251</v>
       </c>
       <c r="G25" t="n">
-        <v>0.129568352739457</v>
+        <v>0.1274668318417579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2187849293539859</v>
+        <v>0.2163726350440982</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +999,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1178704374144319</v>
+        <v>0.1167883667970518</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007252321536902761</v>
+        <v>0.006856710512488774</v>
       </c>
       <c r="D26" t="n">
-        <v>29.46692268445513</v>
+        <v>29.55291811035851</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0496586813913303</v>
+        <v>0.04987027832247474</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1036197730170177</v>
+        <v>0.1033130900963538</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1321211018118469</v>
+        <v>0.1302636434977504</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2211419706806264</v>
+        <v>0.2192393039918585</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1027,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1220811423598562</v>
+        <v>0.1204681811492879</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007146291459685908</v>
+        <v>0.006921069735949779</v>
       </c>
       <c r="D27" t="n">
-        <v>29.11740688913864</v>
+        <v>29.022805397975</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05567456673404157</v>
+        <v>0.0559800275581877</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1080305649009582</v>
+        <v>0.106858354867327</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1361317198187539</v>
+        <v>0.1340780074312483</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2253526756260506</v>
+        <v>0.2229191183440946</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1055,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1232720042135041</v>
+        <v>0.1240921920006351</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00716153581725948</v>
+        <v>0.006860681104448828</v>
       </c>
       <c r="D28" t="n">
-        <v>26.16275451701625</v>
+        <v>26.61603772104083</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08403230770418317</v>
+        <v>0.08315393964962313</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1091963941166053</v>
+        <v>0.1106060396820269</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1373476143104025</v>
+        <v>0.137578344319245</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2265435374796985</v>
+        <v>0.2265431291954418</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1083,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01434479949641376</v>
+        <v>0.004389932345088535</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001418444108487877</v>
+        <v>0.0005917679427050617</v>
       </c>
       <c r="D29" t="n">
-        <v>2.575276824397787</v>
+        <v>1.626318212158945</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00891385920699507</v>
+        <v>0.004642694544901384</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01156192527061761</v>
+        <v>0.003227804269728553</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01712767372220998</v>
+        <v>0.005552060420448549</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1176163327626082</v>
+        <v>0.1068408695398952</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year17final.xlsx
+++ b/hourly datasets/cap_gen_year17final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2235123242894051</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1024509371948067</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09735331366884051</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1251618907786477</v>
+        <v>0.388739380487556</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2276128279734544</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2625803698669914</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1409700663108019</v>
+        <v>0.4042956448603932</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2434210035056086</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2781366342398285</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03931045717140182</v>
+        <v>0.4578431318486458</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004286792376561793</v>
+        <v>0.01581553369581232</v>
       </c>
       <c r="D5" t="n">
-        <v>7.860018660693552</v>
+        <v>7.908914839346393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04858863438849403</v>
+        <v>0.2279294153181616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03090282406336579</v>
+        <v>0.001038599510559495</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04771809027943816</v>
+        <v>0.06305328540897594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1417613943662085</v>
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3316841212280812</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +576,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0272529923045134</v>
+        <v>0.3683712103256203</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +584,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1297039294993201</v>
+        <v>31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2422121997050557</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009373491403090836</v>
+        <v>0.3087695752153198</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001078042523813238</v>
+        <v>0.007466172419228406</v>
       </c>
       <c r="D7" t="n">
-        <v>2.239829610691232</v>
+        <v>-3.073675805083198</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004626182562008549</v>
+        <v>0.00483515598240523</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007254812198671192</v>
+        <v>-0.04470679855209273</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01149217060751044</v>
+        <v>-0.01535407329915438</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1118244285978975</v>
+        <v>31</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1826105645947552</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007732666289601032</v>
+        <v>0.3117320294609877</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001051449239383792</v>
+        <v>0.007833899436624814</v>
       </c>
       <c r="D8" t="n">
-        <v>1.923073323159804</v>
+        <v>-2.742425823742507</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003703679840398062</v>
+        <v>0.003888404557554618</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005668510802046192</v>
+        <v>-0.04366743944524031</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009796821777155988</v>
+        <v>-0.01287373635380982</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1101836034844077</v>
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1855730188404231</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002496623643887608</v>
+        <v>0.3096883554105773</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00097438860492936</v>
+        <v>0.01000000871403673</v>
       </c>
       <c r="D9" t="n">
-        <v>1.262063716918347</v>
+        <v>-2.487995085163463</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00274644758770072</v>
+        <v>0.00287428233066677</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0005818982634786801</v>
+        <v>-0.05605530754559013</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004411349024296561</v>
+        <v>-0.01673859707518709</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1049475608386943</v>
+        <v>31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1835293447900126</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002488961979316782</v>
+        <v>0.3110108525859924</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001101856956930826</v>
+        <v>0.01193128253472688</v>
       </c>
       <c r="D10" t="n">
-        <v>1.338429213075876</v>
+        <v>-1.618152735662278</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002858187573231679</v>
+        <v>0.003492935140643408</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003243229445220957</v>
+        <v>-0.05807008640346958</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004653601014111524</v>
+        <v>-0.01116128513445768</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1049398991741235</v>
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1848518419654278</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02958425060836664</v>
+        <v>0.2730301853516152</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1320351878031733</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1468711747310505</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05239004873669086</v>
+        <v>0.300066115081787</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1548409859314976</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1739071044612224</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06683705317371819</v>
+        <v>0.314487779879384</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1692879903685249</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1883287692588194</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07760570208109278</v>
+        <v>0.3265604926023258</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1800566392758995</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2004014819817612</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08287245049233326</v>
+        <v>0.3351288164777407</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.18532338768714</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2089698058571761</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08797747845923434</v>
+        <v>0.3394399457060711</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.190428415654041</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2132809350855065</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09169169449991302</v>
+        <v>0.3434283843660302</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1941426316947197</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2172693737454656</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1024509371948067</v>
+        <v>0.1261590106205646</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008618418715896685</v>
+        <v>0.00862543697217999</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.87795558944316</v>
+        <v>-18.8933285174476</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0283273034693172</v>
+        <v>0.0283503713060186</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1193752552478169</v>
+        <v>-0.1194724663677256</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08552661914179618</v>
+        <v>-0.08559626622578788</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09205560835761636</v>
+        <v>0.3444834940156105</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1945065455524231</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2183244833950458</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09515115887834853</v>
+        <v>0.3479213565275985</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1976020960731552</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2217623459070339</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09944049037465662</v>
+        <v>0.353230741548941</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2018914275694633</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2270717309283763</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +962,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1035047637157237</v>
+        <v>0.358161543073778</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +970,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2059557009105304</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2320025324532133</v>
       </c>
     </row>
     <row r="23">
@@ -915,25 +983,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1077829928986616</v>
+        <v>0.3635684872516775</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006749219018021481</v>
+        <v>0.006744530971519341</v>
       </c>
       <c r="D23" t="n">
-        <v>27.09652401640841</v>
+        <v>27.07644741100233</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04262004030880342</v>
+        <v>0.04258974773803621</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09451233458833359</v>
+        <v>0.09443451924161404</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1210536512089894</v>
+        <v>0.120957424939798</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2102339300934683</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2374094766311129</v>
       </c>
     </row>
     <row r="24">
@@ -943,25 +1014,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1116297935099695</v>
+        <v>0.3692824570664683</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006717705687251152</v>
+        <v>0.00671154928748002</v>
       </c>
       <c r="D24" t="n">
-        <v>27.94997700172785</v>
+        <v>27.92233235140445</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03005962000518489</v>
+        <v>0.0300442101492701</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09841973565885995</v>
+        <v>0.09831118764053672</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1248398513610787</v>
+        <v>0.12470712918066</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2140807307047762</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2431234464459037</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +1045,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1139216978492915</v>
+        <v>0.3729137142174869</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006884768854934427</v>
+        <v>0.006875124903040823</v>
       </c>
       <c r="D25" t="n">
-        <v>29.07659349030482</v>
+        <v>29.03382030528742</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04713455382755396</v>
+        <v>0.04708749620740375</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1003765638568251</v>
+        <v>0.1001894514242558</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1274668318417579</v>
+        <v>0.127241858434436</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2163726350440982</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2467547035969223</v>
       </c>
     </row>
     <row r="26">
@@ -999,25 +1076,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1167883667970518</v>
+        <v>0.3780242612123146</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006856710512488774</v>
+        <v>0.00684368708488305</v>
       </c>
       <c r="D26" t="n">
-        <v>29.55291811035851</v>
+        <v>29.49801358176212</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04987027832247474</v>
+        <v>0.04980278646682476</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1033130900963538</v>
+        <v>0.1030590946320679</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1302636434977504</v>
+        <v>0.129958528180497</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2192393039918585</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.25186525059175</v>
       </c>
     </row>
     <row r="27">
@@ -1027,25 +1107,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1204681811492879</v>
+        <v>0.382793437267678</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006921069735949779</v>
+        <v>0.006904117967684998</v>
       </c>
       <c r="D27" t="n">
-        <v>29.022805397975</v>
+        <v>28.95561465781753</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0559800275581877</v>
+        <v>0.055873215297148</v>
       </c>
       <c r="F27" t="n">
-        <v>0.106858354867327</v>
+        <v>0.1065211299283279</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1340780074312483</v>
+        <v>0.1336742374293076</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2229191183440946</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2566344266471134</v>
       </c>
     </row>
     <row r="28">
@@ -1055,25 +1138,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1240921920006351</v>
+        <v>0.3915891525736138</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006860681104448828</v>
+        <v>0.006866267978312386</v>
       </c>
       <c r="D28" t="n">
-        <v>26.61603772104083</v>
+        <v>26.63771201885926</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08315393964962313</v>
+        <v>0.08322165458419123</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1106060396820269</v>
+        <v>0.1106961097469146</v>
       </c>
       <c r="G28" t="n">
-        <v>0.137578344319245</v>
+        <v>0.1376903788015896</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2265431291954418</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2654301419530492</v>
       </c>
     </row>
     <row r="29">
@@ -1083,25 +1169,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.004389932345088535</v>
+        <v>0.3415393009549152</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0005917679427050617</v>
+        <v>0.004555017117800856</v>
       </c>
       <c r="D29" t="n">
-        <v>1.626318212158945</v>
+        <v>-0.1594023563903339</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004642694544901384</v>
+        <v>0.03080856022401344</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003227804269728553</v>
+        <v>-0.01273273427680165</v>
       </c>
       <c r="G29" t="n">
-        <v>0.005552060420448549</v>
+        <v>0.005174250946470671</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1068408695398952</v>
+        <v>31</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2153802903343506</v>
       </c>
     </row>
   </sheetData>
